--- a/artfynd/A 52039-2021 artfynd.xlsx
+++ b/artfynd/A 52039-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52039-2021 artfynd.xlsx
+++ b/artfynd/A 52039-2021 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100976283</v>
+        <v>119439306</v>
       </c>
       <c r="B2" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,31 +708,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalhygge 2022 Karsholm, Sk</t>
+          <t>Sixtorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455791.8203119535</v>
+        <v>455672</v>
       </c>
       <c r="R2" t="n">
-        <v>6215894.904950112</v>
+        <v>6215756</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,22 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,51 +768,49 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mattias Göransson</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Göransson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Engla Grönvall</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Alight - Karsholm fågelinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119439306</v>
+        <v>119438376</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -858,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455672</v>
+        <v>455679</v>
       </c>
       <c r="R3" t="n">
-        <v>6215756</v>
+        <v>6215798</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,37 +905,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119438376</v>
+        <v>100976283</v>
       </c>
       <c r="B4" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -962,29 +938,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sixtorp, Sk</t>
+          <t>Kalhygge 2022 Karsholm, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455679</v>
+        <v>455791</v>
       </c>
       <c r="R4" t="n">
-        <v>6215798</v>
+        <v>6215895</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,12 +986,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2022-05-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2022-05-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,25 +1000,22 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Mattias Göransson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Alight - Karsholm fågelinventering</t>
-        </is>
-      </c>
+          <t>Mattias Göransson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52039-2021 artfynd.xlsx
+++ b/artfynd/A 52039-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119439306</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119438376</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,8 +1031,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100976283</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>